--- a/output/pdf_financials_xlsx/AMCO.xlsx
+++ b/output/pdf_financials_xlsx/AMCO.xlsx
@@ -6325,34 +6325,34 @@
         <v>0.017055</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.018163</v>
+        <v>0.017055</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.225398</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.302366</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.233688</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.291432</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.263328</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.134826</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.134826</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.30065</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.30065</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.923963</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.990735</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.95976</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.892988</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.422595</v>
       </c>
     </row>
     <row r="93">
@@ -8004,10 +8004,10 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.005146</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.023858</v>
       </c>
       <c r="M118" s="1" t="inlineStr">
         <is>
@@ -8015,19 +8015,19 @@
         </is>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.24</v>
+        <v>-3.441715</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>1.654259</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>1.871766</v>
+        <v>-1.094279</v>
       </c>
       <c r="Q118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.004501</v>
       </c>
     </row>
     <row r="119">
@@ -10446,7 +10446,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -13493,7 +13497,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -15544,7 +15552,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16510,7 +16522,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -17540,7 +17556,11 @@
           <t>Reserves (Note 6) 1,037,360</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -18631,7 +18651,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -19940,7 +19964,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -20841,7 +20869,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -21756,7 +21788,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -22986,7 +23022,11 @@
           <t>Reserves (Note 6) 225,398</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -25360,7 +25400,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -27653,7 +27697,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AMCO.xlsx
+++ b/output/pdf_financials_xlsx/AMCO.xlsx
@@ -2680,37 +2680,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.351244</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.351244</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.48465</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.257805</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.13797</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.060635</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.438172</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.014453</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.40486</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.436408</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.211477</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2718,19 +2718,19 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.054236</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.772108</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.142704</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.023037</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.299514</v>
       </c>
     </row>
     <row r="35">
@@ -2800,37 +2800,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.351244</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.351244</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.48465</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.257805</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.13797</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.060635</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.438172</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.014453</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.40486</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.436408</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.211477</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.054236</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.772108</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.142704</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.023037</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.299514</v>
       </c>
     </row>
     <row r="37">
@@ -3520,37 +3520,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.351244</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.34369</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.55529</v>
+        <v>0.07063999999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.257805</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.143488</v>
+        <v>0.005518</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06446</v>
+        <v>0.003825</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.571922</v>
+        <v>0.13375</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.148203</v>
+        <v>0.13375</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.40486</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.447894</v>
+        <v>0.011486</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.213066</v>
+        <v>0.001589</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3558,19 +3558,19 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.093163</v>
+        <v>0.038927</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.829752</v>
+        <v>0.057644</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.165078</v>
+        <v>0.022374</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.045341</v>
+        <v>0.022304</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.635587</v>
+        <v>0.336073</v>
       </c>
     </row>
     <row r="49">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -22198,7 +22198,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
